--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487049_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487049_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7424</v>
+        <v>5.4773</v>
       </c>
       <c r="E2" t="n">
-        <v>3.152</v>
+        <v>3.8669</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5904</v>
+        <v>1.6103</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2645</v>
+        <v>1.7301</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8651</v>
+        <v>1.0268</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6005</v>
+        <v>0.7033</v>
       </c>
       <c r="J2" t="n">
-        <v>1.011</v>
+        <v>1.7097</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2377</v>
+        <v>0.9936</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7733</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7464</v>
+        <v>0.0203</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6273</v>
+        <v>0.0332</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3738</v>
+        <v>-0.0129</v>
       </c>
       <c r="P2" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>3.613</v>
+        <v>-0.4458</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5343</v>
+        <v>-0.2987</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0787</v>
+        <v>-0.1471</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8999</v>
+        <v>2.4559</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5717</v>
+        <v>2.4559</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8834</v>
+        <v>3.7773</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4069</v>
+        <v>1.6687</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4765</v>
+        <v>2.1086</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7301</v>
+        <v>0.2645</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0268</v>
+        <v>0.8651</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7033</v>
+        <v>-0.6005</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7097</v>
+        <v>1.011</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9936</v>
+        <v>0.2377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.7733</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0203</v>
+        <v>-0.7464</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0332</v>
+        <v>0.6273</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0129</v>
+        <v>-1.3738</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0397</v>
+        <v>1.6478</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7588</v>
+        <v>1.051</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2809</v>
+        <v>0.5968</v>
       </c>
       <c r="V3" t="n">
-        <v>2.4559</v>
+        <v>0.8999</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4559</v>
+        <v>0.5717</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5625</v>
+        <v>3.743</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7039</v>
+        <v>1.8041</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8586</v>
+        <v>1.9389</v>
       </c>
       <c r="G4" t="n">
         <v>2.7746</v>
@@ -766,13 +766,13 @@
         <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3946</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1018</v>
+        <v>0.202</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2928</v>
+        <v>0.3731</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5717</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NDIAYE SOW</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2189</v>
+        <v>3.373</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6153</v>
+        <v>1.4566</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6036</v>
+        <v>1.9164</v>
       </c>
       <c r="G5" t="n">
-        <v>2.012</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2451</v>
+        <v>2.485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7669</v>
+        <v>-1.7144</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4511</v>
+        <v>0.9166</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6778</v>
+        <v>1.3971</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7733</v>
+        <v>-0.4805</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5609</v>
+        <v>-0.1459</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5673</v>
+        <v>1.0879</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0064</v>
+        <v>-1.2338</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>2.1231</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5441</v>
+        <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5579</v>
+        <v>0.4792</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3424</v>
+        <v>0.2542</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2155</v>
+        <v>0.225</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1857</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4716</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2859</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>M. NDIAYE SOW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.318</v>
+        <v>3.3725</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6961000000000001</v>
+        <v>1.7154</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6219</v>
+        <v>1.6571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7707000000000001</v>
+        <v>2.012</v>
       </c>
       <c r="H6" t="n">
-        <v>2.485</v>
+        <v>1.2451</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7144</v>
+        <v>0.7669</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9166</v>
+        <v>1.4511</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3971</v>
+        <v>0.6778</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4805</v>
+        <v>0.7733</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1459</v>
+        <v>0.5609</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0879</v>
+        <v>0.5673</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2338</v>
+        <v>-0.0064</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1231</v>
+        <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5757</v>
+        <v>-0.4042</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5063</v>
+        <v>-0.2422</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0694</v>
+        <v>-0.162</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.1857</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>1.4716</v>
       </c>
       <c r="X6" t="n">
         <v>-0.2859</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>M. ERRASTI UGARTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1784</v>
+        <v>1.7501</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1543</v>
+        <v>1.5478</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0241</v>
+        <v>0.2023</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1795</v>
+        <v>0.396</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2463</v>
+        <v>1.1758</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9332</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0535</v>
+        <v>1.0964</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9472</v>
+        <v>1.0557</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1064</v>
+        <v>0.0407</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.126</v>
+        <v>-0.7003</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7008</v>
+        <v>0.1201</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8268</v>
+        <v>-0.8204</v>
       </c>
       <c r="P7" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6934</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0873</v>
+        <v>0.4515</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6061</v>
+        <v>0.2234</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0856</v>
+        <v>-0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0856</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ERRASTI UGARTE</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1368</v>
+        <v>1.7422</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1487</v>
+        <v>0.1731</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0119</v>
+        <v>1.569</v>
       </c>
       <c r="G8" t="n">
-        <v>0.396</v>
+        <v>-1.1795</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1758</v>
+        <v>-0.2463</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.9332</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0964</v>
+        <v>-1.0535</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0557</v>
+        <v>-0.9472</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0407</v>
+        <v>-0.1064</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7003</v>
+        <v>-0.126</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1201</v>
+        <v>0.7008</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8204</v>
+        <v>-0.8268</v>
       </c>
       <c r="P8" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0616</v>
+        <v>0.2571</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0523</v>
+        <v>0.1061</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0092</v>
+        <v>0.151</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2859</v>
+        <v>2.0856</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.0856</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.692</v>
+        <v>1.7247</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9496</v>
+        <v>-0.6492</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6416</v>
+        <v>2.3739</v>
       </c>
       <c r="G9" t="n">
         <v>0.3088</v>
@@ -1156,13 +1156,13 @@
         <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1203</v>
+        <v>0.153</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3424</v>
+        <v>-0.042</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4627</v>
+        <v>0.195</v>
       </c>
       <c r="V9" t="n">
         <v>1.842</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6089</v>
+        <v>1.5217</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2762</v>
+        <v>-1.1761</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8852</v>
+        <v>2.6978</v>
       </c>
       <c r="G10" t="n">
         <v>1.2725</v>
@@ -1234,13 +1234,13 @@
         <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2426</v>
+        <v>-0.3298</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4019</v>
+        <v>-0.3017</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1593</v>
+        <v>-0.0281</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4467</v>
+        <v>-0.4721</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5956</v>
+        <v>-0.0761</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8511</v>
+        <v>-0.396</v>
       </c>
       <c r="G11" t="n">
         <v>1.1422</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3959</v>
+        <v>0.5787</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0766</v>
+        <v>0.4429</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3193</v>
+        <v>0.1358</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3507</v>
+        <v>-1.8709</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.575</v>
+        <v>-2.2558</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2243</v>
+        <v>0.3849</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3143</v>
@@ -1390,13 +1390,13 @@
         <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8434</v>
+        <v>-0.3635</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4019</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4416</v>
+        <v>-0.2809</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.5439</v>
+        <v>24.1388</v>
       </c>
       <c r="E13" t="n">
-        <v>7.480800000000001</v>
+        <v>8.075399999999998</v>
       </c>
       <c r="F13" t="n">
         <v>16.0632</v>
@@ -1459,7 +1459,7 @@
         <v>-6.901</v>
       </c>
       <c r="P13" t="n">
-        <v>6.7552</v>
+        <v>6.755200000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.6152</v>
@@ -1468,13 +1468,13 @@
         <v>17.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2277</v>
+        <v>2.8225</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9454000000000002</v>
+        <v>1.5405</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2821</v>
+        <v>1.282</v>
       </c>
       <c r="V13" t="n">
         <v>6.383500000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5364</v>
+        <v>1.2843</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1267</v>
+        <v>1.5273</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5903</v>
+        <v>-0.243</v>
       </c>
       <c r="G14" t="n">
         <v>2.1121</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6386</v>
+        <v>-0.8907</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1012</v>
+        <v>-0.7006</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5374</v>
+        <v>-0.1901</v>
       </c>
       <c r="V14" t="n">
         <v>0.4489</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. SAGASTI ARGOTE</t>
+          <t>M. ZUBIZARRETA ALBIZU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5121</v>
+        <v>0.604</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8412</v>
+        <v>-0.0473</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3291</v>
+        <v>0.6514</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6296</v>
+        <v>0.7423</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6956</v>
+        <v>-1.3661</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3252</v>
+        <v>2.1085</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5305</v>
+        <v>0.7419</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3416</v>
+        <v>-1.2524</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8722</v>
+        <v>1.9943</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9009</v>
+        <v>0.0005</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3539</v>
+        <v>-0.1137</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5469000000000001</v>
+        <v>0.1142</v>
       </c>
       <c r="P15" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7244</v>
+        <v>0.1775</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5037</v>
+        <v>0.1759</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2208</v>
+        <v>0.0016</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.228</v>
+        <v>-0.1228</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ZUBIZARRETA ALBIZU</t>
+          <t>I. SAGASTI ARGOTE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1496</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0473</v>
+        <v>1.4406</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1969</v>
+        <v>-1.3562</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7423</v>
+        <v>0.6296</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3661</v>
+        <v>-0.6956</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1085</v>
+        <v>1.3252</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7419</v>
+        <v>1.5305</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2524</v>
+        <v>-0.3416</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9943</v>
+        <v>1.8722</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0005</v>
+        <v>-0.9009</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1137</v>
+        <v>-0.3539</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1142</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P16" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.193</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.965</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2769</v>
+        <v>0.2968</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1759</v>
+        <v>0.1031</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4528</v>
+        <v>0.1937</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1228</v>
+        <v>-1.228</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1228</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. EGUSKITZA AGINALDE</t>
+          <t>A. OLIVEIRA GETE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8745000000000001</v>
+        <v>-0.4441</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3734</v>
+        <v>0.0226</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4989</v>
+        <v>-0.4667</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5517</v>
+        <v>-0.7312</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0455</v>
+        <v>-1.1189</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5062</v>
+        <v>0.3877</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0893</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0414</v>
+        <v>-0.7247</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0407</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6338</v>
+        <v>-0.8205</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.3942</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.4263</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.772</v>
+        <v>0.772</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2492</v>
+        <v>-0.3199</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2974</v>
+        <v>-0.0244</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0482</v>
+        <v>-0.2955</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6985</v>
+        <v>-0.165</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6985</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. OLIVEIRA GETE</t>
+          <t>A. EGUSKITZA AGINALDE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9121</v>
+        <v>-0.6474</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2229</v>
+        <v>-1.1731</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.135</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7312</v>
+        <v>-0.5517</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1189</v>
+        <v>-0.0455</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3877</v>
+        <v>-0.5062</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0893</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7247</v>
+        <v>0.0414</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.0407</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8205</v>
+        <v>-0.6338</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3942</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4263</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.772</v>
+        <v>-0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7879</v>
+        <v>-0.0221</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1759</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9637</v>
+        <v>0.075</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.165</v>
+        <v>0.6985</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1228</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2309</v>
+        <v>-0.984</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4053</v>
+        <v>-0.1049</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8256</v>
+        <v>-0.8791</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1457</v>
@@ -1936,13 +1936,13 @@
         <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2432</v>
+        <v>0.0036</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5354</v>
+        <v>-0.235</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2921</v>
+        <v>0.2386</v>
       </c>
       <c r="V19" t="n">
         <v>-0.614</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1185</v>
+        <v>-2.4599</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6476</v>
+        <v>-1.7477</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.471</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0622</v>
@@ -2014,13 +2014,13 @@
         <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5526</v>
+        <v>0.2112</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2102</v>
+        <v>-0.3103</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7627</v>
+        <v>0.5215</v>
       </c>
       <c r="V20" t="n">
         <v>0.1631</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ARTECHE URRUZOLA</t>
+          <t>M. LARRAÑAGA ORMAZABAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3655</v>
+        <v>-3.0414</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.6691</v>
+        <v>-1.9924</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3035</v>
+        <v>-1.049</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2974</v>
+        <v>-1.6256</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.8008</v>
+        <v>-0.0041</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5034</v>
+        <v>-1.6215</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1124</v>
+        <v>-0.5848</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.2345</v>
+        <v>0.0828</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1221</v>
+        <v>-0.6676</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8149999999999999</v>
+        <v>-1.0408</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4338</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3813</v>
+        <v>-0.9539</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.0881</v>
+        <v>-0.772</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8602</v>
+        <v>-1.3511</v>
       </c>
       <c r="R21" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="S21" t="n">
-        <v>2.02</v>
+        <v>0.2561</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3035</v>
+        <v>-0.0565</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7165</v>
+        <v>0.3126</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. LARRAÑAGA ORMAZABAL</t>
+          <t>E. ANDRES CAMPOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3953</v>
+        <v>-3.2481</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2928</v>
+        <v>-2.5963</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1026</v>
+        <v>-0.6518</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6256</v>
+        <v>-1.9189</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0041</v>
+        <v>-1.1799</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6215</v>
+        <v>-0.739</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5848</v>
+        <v>-0.5241</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0828</v>
+        <v>-0.6055</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6676</v>
+        <v>0.0814</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0408</v>
+        <v>-1.3948</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.5743</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9539</v>
+        <v>-0.8204</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.772</v>
+        <v>-0.965</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.3511</v>
+        <v>-1.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0978</v>
+        <v>-0.3642</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3569</v>
+        <v>-0.1421</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2591</v>
+        <v>-0.2221</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. ANDRES CAMPOS</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8225</v>
+        <v>-3.643</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7966</v>
+        <v>-1.726</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0259</v>
+        <v>-1.917</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9189</v>
+        <v>-0.5513</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1799</v>
+        <v>-0.5577</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.739</v>
+        <v>0.0064</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5241</v>
+        <v>-0.532</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6055</v>
+        <v>-0.5641</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0814</v>
+        <v>0.0321</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3948</v>
+        <v>-0.0194</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5743</v>
+        <v>0.0064</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8204</v>
+        <v>-0.0257</v>
       </c>
       <c r="P23" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-1.9301</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.965</v>
+        <v>1.158</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9386</v>
+        <v>-0.42</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3424</v>
+        <v>-0.229</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5962</v>
+        <v>-0.191</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.8646</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.8646</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1036</v>
+        <v>-4.177</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7953</v>
+        <v>-2.8955</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3083</v>
+        <v>-1.2815</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7776999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>0.386</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4039</v>
+        <v>0.3305</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1322</v>
+        <v>0.0321</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2716</v>
+        <v>0.2984</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7997</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>I. ARTECHE URRUZOLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.919</v>
+        <v>-4.869</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2267</v>
+        <v>-6.7706</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6923</v>
+        <v>1.9017</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5513</v>
+        <v>-2.2974</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5577</v>
+        <v>-2.8008</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0064</v>
+        <v>0.5034</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.532</v>
+        <v>-3.1124</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.5641</v>
+        <v>-3.2345</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0321</v>
+        <v>0.1221</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0194</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0064</v>
+        <v>0.4338</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0257</v>
+        <v>0.3813</v>
       </c>
       <c r="P25" t="n">
-        <v>0.193</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R25" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6961</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7297</v>
+        <v>0.202</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9664</v>
+        <v>0.3146</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.8646</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.8646</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-23.5438</v>
+        <v>-21.5411</v>
       </c>
       <c r="E26" t="n">
         <v>-16.0633</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.4808</v>
+        <v>-5.4777</v>
       </c>
       <c r="G26" t="n">
         <v>-8.1777</v>
@@ -2452,25 +2452,25 @@
         <v>-10.1483</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9706</v>
+        <v>1.970599999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2603999999999996</v>
+        <v>0.2604000000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.6406</v>
+        <v>-6.640600000000001</v>
       </c>
       <c r="L26" t="n">
         <v>6.9012</v>
       </c>
       <c r="M26" t="n">
-        <v>-8.438000000000001</v>
+        <v>-8.437999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>-3.5074</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.9303</v>
+        <v>-4.930299999999999</v>
       </c>
       <c r="P26" t="n">
         <v>-6.7552</v>
@@ -2482,13 +2482,13 @@
         <v>10.6152</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.2274</v>
+        <v>-0.2246000000000001</v>
       </c>
       <c r="T26" t="n">
         <v>-1.282</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9454999999999998</v>
+        <v>1.0573</v>
       </c>
       <c r="V26" t="n">
         <v>-6.3835</v>
